--- a/artfynd/A 25180-2025 artfynd.xlsx
+++ b/artfynd/A 25180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821250</v>
+        <v>132821229</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566621</v>
+        <v>566708</v>
       </c>
       <c r="R2" t="n">
-        <v>7220878</v>
+        <v>7221120</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821228</v>
+        <v>132821221</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566709</v>
+        <v>566576</v>
       </c>
       <c r="R3" t="n">
-        <v>7221118</v>
+        <v>7221137</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132821220</v>
+        <v>132821224</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566576</v>
+        <v>566600</v>
       </c>
       <c r="R4" t="n">
-        <v>7221138</v>
+        <v>7221120</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132821229</v>
+        <v>132821226</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566708</v>
+        <v>566605</v>
       </c>
       <c r="R5" t="n">
-        <v>7221120</v>
+        <v>7221114</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132821252</v>
+        <v>132821227</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566608</v>
+        <v>566662</v>
       </c>
       <c r="R6" t="n">
-        <v>7220918</v>
+        <v>7221081</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:32</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:32</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132821255</v>
+        <v>132821228</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566576</v>
+        <v>566709</v>
       </c>
       <c r="R7" t="n">
-        <v>7220958</v>
+        <v>7221118</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132821223</v>
+        <v>132821230</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566597</v>
+        <v>566755</v>
       </c>
       <c r="R8" t="n">
-        <v>7221118</v>
+        <v>7221123</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132821226</v>
+        <v>132821232</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1469,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566605</v>
+        <v>566848</v>
       </c>
       <c r="R9" t="n">
-        <v>7221114</v>
+        <v>7221098</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,50 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132821249</v>
+        <v>132821233</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566621</v>
+        <v>566871</v>
       </c>
       <c r="R10" t="n">
-        <v>7220876</v>
+        <v>7221055</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1616,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>06:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132821224</v>
+        <v>132821250</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1688,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566600</v>
+        <v>566621</v>
       </c>
       <c r="R11" t="n">
-        <v>7221120</v>
+        <v>7220878</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1723,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132821230</v>
+        <v>132821252</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1795,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566755</v>
+        <v>566608</v>
       </c>
       <c r="R12" t="n">
-        <v>7221123</v>
+        <v>7220918</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1830,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>05:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>05:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132821233</v>
+        <v>132821253</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1902,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566871</v>
+        <v>566598</v>
       </c>
       <c r="R13" t="n">
-        <v>7221055</v>
+        <v>7220940</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1937,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>06:13</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132821256</v>
+        <v>132821257</v>
       </c>
       <c r="B14" t="n">
-        <v>97997</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,14 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132821253</v>
+        <v>132821258</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2116,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566598</v>
+        <v>566568</v>
       </c>
       <c r="R15" t="n">
-        <v>7220940</v>
+        <v>7220968</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2151,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132821258</v>
+        <v>132821255</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>83358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566568</v>
+        <v>566576</v>
       </c>
       <c r="R16" t="n">
-        <v>7220968</v>
+        <v>7220958</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2258,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132821257</v>
+        <v>132821223</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566574</v>
+        <v>566597</v>
       </c>
       <c r="R17" t="n">
-        <v>7220955</v>
+        <v>7221118</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2365,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:26</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:26</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132821227</v>
+        <v>132821220</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,34 +2403,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566662</v>
+        <v>566576</v>
       </c>
       <c r="R18" t="n">
-        <v>7221081</v>
+        <v>7221138</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821232</v>
+        <v>132821249</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,34 +2515,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nymyran, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566848</v>
+        <v>566621</v>
       </c>
       <c r="R19" t="n">
-        <v>7221098</v>
+        <v>7220876</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,32 +2616,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821221</v>
+        <v>132821256</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>98060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566576</v>
+        <v>566574</v>
       </c>
       <c r="R20" t="n">
-        <v>7221137</v>
+        <v>7220955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
